--- a/tabela_vendas_ZePequeno_corrigido.xlsx
+++ b/tabela_vendas_ZePequeno_corrigido.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2342" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="80">
   <si>
     <t xml:space="preserve">Data</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">Paçoca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2331.568989</t>
   </si>
   <si>
     <t xml:space="preserve">Blumenau</t>
@@ -613,8 +616,8 @@
       <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>2331</v>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -622,13 +625,13 @@
         <v>45901</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>1514</v>
@@ -656,7 +659,7 @@
         <v>45901</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>6</v>
@@ -673,13 +676,13 @@
         <v>45901</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1430</v>
@@ -690,7 +693,7 @@
         <v>45901</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
@@ -707,10 +710,10 @@
         <v>45901</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>7</v>
@@ -724,13 +727,13 @@
         <v>45901</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>1750</v>
@@ -747,7 +750,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>2710</v>
@@ -778,7 +781,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>7</v>
@@ -792,13 +795,13 @@
         <v>45536</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>2270</v>
@@ -826,13 +829,13 @@
         <v>45536</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>2610</v>
@@ -843,7 +846,7 @@
         <v>45536</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>6</v>
@@ -863,10 +866,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>2740</v>
@@ -877,10 +880,10 @@
         <v>45536</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>7</v>
@@ -894,13 +897,13 @@
         <v>45536</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>2890</v>
@@ -914,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>7</v>
@@ -928,13 +931,13 @@
         <v>45536</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>2350</v>
@@ -945,10 +948,10 @@
         <v>45536</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>7</v>
@@ -968,7 +971,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>0</v>
@@ -979,10 +982,10 @@
         <v>45536</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>7</v>
@@ -996,13 +999,13 @@
         <v>45536</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>2120</v>
@@ -1013,7 +1016,7 @@
         <v>45536</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>6</v>
@@ -1033,7 +1036,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>7</v>
@@ -1047,13 +1050,13 @@
         <v>45536</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>987</v>
@@ -1064,13 +1067,13 @@
         <v>45536</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>1680</v>
@@ -1081,10 +1084,10 @@
         <v>45536</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>7</v>
@@ -1098,13 +1101,13 @@
         <v>45536</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>1390</v>
@@ -1118,7 +1121,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>7</v>
@@ -1135,10 +1138,10 @@
         <v>5</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>2579</v>
@@ -1152,7 +1155,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>7</v>
@@ -1166,13 +1169,13 @@
         <v>45931</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>2271</v>
@@ -1183,13 +1186,13 @@
         <v>45931</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36" s="4" t="n">
         <v>1002</v>
@@ -1203,10 +1206,10 @@
         <v>5</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>1375</v>
@@ -1217,7 +1220,7 @@
         <v>45931</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>6</v>
@@ -1237,10 +1240,10 @@
         <v>5</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>1709</v>
@@ -1251,13 +1254,13 @@
         <v>45931</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>2732</v>
@@ -1268,7 +1271,7 @@
         <v>45931</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>6</v>
@@ -1285,13 +1288,13 @@
         <v>45931</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42" s="4" t="n">
         <v>1995</v>
@@ -1308,7 +1311,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43" s="4" t="n">
         <v>2143</v>
@@ -1322,7 +1325,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>7</v>
@@ -1336,10 +1339,10 @@
         <v>45931</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>7</v>
@@ -1356,10 +1359,10 @@
         <v>5</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E46" s="4" t="n">
         <v>1389</v>
@@ -1373,7 +1376,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>7</v>
@@ -1387,7 +1390,7 @@
         <v>45931</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>6</v>
@@ -1421,13 +1424,13 @@
         <v>45931</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" s="4" t="n">
         <v>2630</v>
@@ -1472,10 +1475,10 @@
         <v>45931</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>7</v>
@@ -1489,13 +1492,13 @@
         <v>45931</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>2470</v>
@@ -1506,13 +1509,13 @@
         <v>45931</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E55" s="4" t="n">
         <v>2650</v>
@@ -1523,13 +1526,13 @@
         <v>45566</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>2180</v>
@@ -1540,10 +1543,10 @@
         <v>45566</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>7</v>
@@ -1563,7 +1566,7 @@
         <v>6</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E58" s="4" t="n">
         <v>2490</v>
@@ -1574,10 +1577,10 @@
         <v>45566</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>7</v>
@@ -1591,13 +1594,13 @@
         <v>45566</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>2670</v>
@@ -1608,13 +1611,13 @@
         <v>45566</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E61" s="4" t="n">
         <v>1540</v>
@@ -1625,13 +1628,13 @@
         <v>45566</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E62" s="4" t="n">
         <v>2810</v>
@@ -1642,10 +1645,10 @@
         <v>45566</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>7</v>
@@ -1665,7 +1668,7 @@
         <v>6</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>2340</v>
@@ -1676,10 +1679,10 @@
         <v>45566</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>7</v>
@@ -1693,13 +1696,13 @@
         <v>45566</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>2200</v>
@@ -1710,10 +1713,10 @@
         <v>45566</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>7</v>
@@ -1730,10 +1733,10 @@
         <v>5</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>2560</v>
@@ -1744,7 +1747,7 @@
         <v>45566</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>6</v>
@@ -1761,7 +1764,7 @@
         <v>45566</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>6</v>
@@ -1778,13 +1781,13 @@
         <v>45566</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4" t="n">
         <v>1580</v>
@@ -1801,7 +1804,7 @@
         <v>6</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E72" s="4" t="n">
         <v>2850</v>
@@ -1812,13 +1815,13 @@
         <v>45566</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>1470</v>
@@ -1829,7 +1832,7 @@
         <v>45566</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>6</v>
@@ -1846,7 +1849,7 @@
         <v>45962</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>6</v>
@@ -1863,13 +1866,13 @@
         <v>45962</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="4" t="n">
         <v>2549</v>
@@ -1883,7 +1886,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>7</v>
@@ -1900,7 +1903,7 @@
         <v>5</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>7</v>
@@ -1917,10 +1920,10 @@
         <v>5</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>2977</v>
@@ -1931,7 +1934,7 @@
         <v>45962</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>6</v>
@@ -1951,7 +1954,7 @@
         <v>5</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>7</v>
@@ -1965,7 +1968,7 @@
         <v>45962</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>6</v>
@@ -1982,13 +1985,13 @@
         <v>45962</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>1242</v>
@@ -1999,13 +2002,13 @@
         <v>45962</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84" s="4" t="n">
         <v>1376</v>
@@ -2022,7 +2025,7 @@
         <v>6</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4" t="n">
         <v>2979</v>
@@ -2033,10 +2036,10 @@
         <v>45962</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>7</v>
@@ -2050,7 +2053,7 @@
         <v>45962</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>6</v>
@@ -2067,13 +2070,13 @@
         <v>45962</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E88" s="4" t="n">
         <v>0</v>
@@ -2084,13 +2087,13 @@
         <v>45962</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E89" s="4" t="n">
         <v>1620</v>
@@ -2101,13 +2104,13 @@
         <v>45962</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E90" s="4" t="n">
         <v>2980</v>
@@ -2118,7 +2121,7 @@
         <v>45962</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>6</v>
@@ -2135,10 +2138,10 @@
         <v>45962</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>7</v>
@@ -2152,13 +2155,13 @@
         <v>45597</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E93" s="4" t="n">
         <v>2230</v>
@@ -2186,13 +2189,13 @@
         <v>45597</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>2570</v>
@@ -2203,7 +2206,7 @@
         <v>45597</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>6</v>
@@ -2223,10 +2226,10 @@
         <v>5</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E97" s="4" t="n">
         <v>2710</v>
@@ -2254,13 +2257,13 @@
         <v>45597</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E99" s="4" t="n">
         <v>2380</v>
@@ -2271,13 +2274,13 @@
         <v>45597</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E100" s="4" t="n">
         <v>1820</v>
@@ -2291,10 +2294,10 @@
         <v>5</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E101" s="4" t="n">
         <v>2640</v>
@@ -2305,7 +2308,7 @@
         <v>45597</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>6</v>
@@ -2322,13 +2325,13 @@
         <v>45597</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E103" s="4" t="n">
         <v>0</v>
@@ -2356,13 +2359,13 @@
         <v>45597</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E105" s="4" t="n">
         <v>2190</v>
@@ -2373,10 +2376,10 @@
         <v>45597</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>7</v>
@@ -2390,13 +2393,13 @@
         <v>45597</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E107" s="4" t="n">
         <v>2490</v>
@@ -2407,10 +2410,10 @@
         <v>45597</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>7</v>
@@ -2427,7 +2430,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>7</v>
@@ -2441,13 +2444,13 @@
         <v>45597</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E110" s="4" t="n">
         <v>1510</v>
@@ -2458,10 +2461,10 @@
         <v>45597</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>7</v>
@@ -2475,13 +2478,13 @@
         <v>45597</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E112" s="4" t="n">
         <v>2</v>
@@ -2495,7 +2498,7 @@
         <v>5</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>7</v>
@@ -2512,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>7</v>
@@ -2529,10 +2532,10 @@
         <v>5</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E115" s="4" t="n">
         <v>2534</v>
@@ -2546,10 +2549,10 @@
         <v>5</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E116" s="4" t="n">
         <v>2186</v>
@@ -2600,7 +2603,7 @@
         <v>6</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E119" s="4" t="n">
         <v>2667</v>
@@ -2617,7 +2620,7 @@
         <v>6</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E120" s="4" t="n">
         <v>1581</v>
@@ -2628,10 +2631,10 @@
         <v>46082</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>7</v>
@@ -2645,10 +2648,10 @@
         <v>46082</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>7</v>
@@ -2662,13 +2665,13 @@
         <v>46082</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E123" s="4" t="n">
         <v>2361</v>
@@ -2679,13 +2682,13 @@
         <v>46082</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E124" s="4" t="n">
         <v>2078</v>
@@ -2696,7 +2699,7 @@
         <v>46082</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>6</v>
@@ -2713,7 +2716,7 @@
         <v>46082</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>6</v>
@@ -2730,13 +2733,13 @@
         <v>46082</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E127" s="4" t="n">
         <v>2226</v>
@@ -2747,13 +2750,13 @@
         <v>46082</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E128" s="4" t="n">
         <v>1842</v>
@@ -2764,10 +2767,10 @@
         <v>46082</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>7</v>
@@ -2781,10 +2784,10 @@
         <v>46082</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>7</v>
@@ -2798,13 +2801,13 @@
         <v>46082</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E131" s="4" t="n">
         <v>2513</v>
@@ -2815,13 +2818,13 @@
         <v>46082</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E132" s="4" t="n">
         <v>2147</v>
@@ -2832,7 +2835,7 @@
         <v>46082</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>6</v>
@@ -2849,7 +2852,7 @@
         <v>46082</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>6</v>
@@ -2866,13 +2869,13 @@
         <v>46082</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E135" s="4" t="n">
         <v>2298</v>
@@ -2883,13 +2886,13 @@
         <v>46082</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E136" s="4" t="n">
         <v>1761</v>
@@ -2900,10 +2903,10 @@
         <v>45717</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>7</v>
@@ -2920,7 +2923,7 @@
         <v>5</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>7</v>
@@ -2934,13 +2937,13 @@
         <v>45717</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E139" s="4" t="n">
         <v>2558</v>
@@ -2951,10 +2954,10 @@
         <v>45717</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>7</v>
@@ -2968,10 +2971,10 @@
         <v>45717</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>7</v>
@@ -2985,10 +2988,10 @@
         <v>45717</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>7</v>
@@ -3002,10 +3005,10 @@
         <v>45717</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>7</v>
@@ -3019,13 +3022,13 @@
         <v>45717</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E144" s="4" t="n">
         <v>500</v>
@@ -3036,13 +3039,13 @@
         <v>45717</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E145" s="4" t="n">
         <v>556</v>
@@ -3087,7 +3090,7 @@
         <v>45352</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>6</v>
@@ -3107,10 +3110,10 @@
         <v>5</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E149" s="4" t="n">
         <v>1680</v>
@@ -3121,7 +3124,7 @@
         <v>45352</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>6</v>
@@ -3138,13 +3141,13 @@
         <v>45352</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E151" s="4" t="n">
         <v>1930</v>
@@ -3155,13 +3158,13 @@
         <v>45352</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E152" s="4" t="n">
         <v>2150</v>
@@ -3172,13 +3175,13 @@
         <v>45352</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E153" s="4" t="n">
         <v>1470</v>
@@ -3189,7 +3192,7 @@
         <v>45352</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>6</v>
@@ -3209,10 +3212,10 @@
         <v>5</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E155" s="4" t="n">
         <v>0</v>
@@ -3223,7 +3226,7 @@
         <v>45352</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>6</v>
@@ -3240,13 +3243,13 @@
         <v>45352</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E157" s="4" t="n">
         <v>890</v>
@@ -3257,7 +3260,7 @@
         <v>45352</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>6</v>
@@ -3280,7 +3283,7 @@
         <v>6</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E159" s="4" t="n">
         <v>1840</v>
@@ -3291,13 +3294,13 @@
         <v>45352</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E160" s="4" t="n">
         <v>2680</v>
@@ -3311,7 +3314,7 @@
         <v>5</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>7</v>
@@ -3325,13 +3328,13 @@
         <v>45352</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E162" s="4" t="n">
         <v>2570</v>
@@ -3342,10 +3345,10 @@
         <v>45352</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>7</v>
@@ -3365,7 +3368,7 @@
         <v>6</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E164" s="4" t="n">
         <v>123456</v>
@@ -3379,7 +3382,7 @@
         <v>5</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>7</v>
@@ -3396,7 +3399,7 @@
         <v>5</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>7</v>
@@ -3413,10 +3416,10 @@
         <v>5</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E167" s="4" t="n">
         <v>1892</v>
@@ -3430,10 +3433,10 @@
         <v>5</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E168" s="4" t="n">
         <v>2553</v>
@@ -3484,7 +3487,7 @@
         <v>6</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E171" s="4" t="n">
         <v>1723</v>
@@ -3501,7 +3504,7 @@
         <v>6</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E172" s="4" t="n">
         <v>2627</v>
@@ -3512,10 +3515,10 @@
         <v>44986</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>7</v>
@@ -3529,10 +3532,10 @@
         <v>44986</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>7</v>
@@ -3546,13 +3549,13 @@
         <v>44986</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E175" s="4" t="n">
         <v>1813</v>
@@ -3563,13 +3566,13 @@
         <v>44986</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E176" s="4" t="n">
         <v>2412</v>
@@ -3580,7 +3583,7 @@
         <v>44986</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>6</v>
@@ -3597,7 +3600,7 @@
         <v>44986</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>6</v>
@@ -3614,13 +3617,13 @@
         <v>44986</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E179" s="4" t="n">
         <v>1537</v>
@@ -3631,13 +3634,13 @@
         <v>44986</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E180" s="4" t="n">
         <v>2338</v>
@@ -3648,10 +3651,10 @@
         <v>44986</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>7</v>
@@ -3665,10 +3668,10 @@
         <v>44986</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>7</v>
@@ -3682,13 +3685,13 @@
         <v>44986</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E183" s="4" t="n">
         <v>1958</v>
@@ -3699,13 +3702,13 @@
         <v>44986</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E184" s="4" t="n">
         <v>2493</v>
@@ -3716,7 +3719,7 @@
         <v>44986</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>6</v>
@@ -3733,7 +3736,7 @@
         <v>44986</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>6</v>
@@ -3750,13 +3753,13 @@
         <v>44986</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E187" s="4" t="n">
         <v>1638</v>
@@ -3767,13 +3770,13 @@
         <v>44986</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E188" s="4" t="n">
         <v>2429</v>
@@ -3784,10 +3787,10 @@
         <v>45778</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>7</v>
@@ -3818,7 +3821,7 @@
         <v>45778</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>6</v>
@@ -3835,10 +3838,10 @@
         <v>45778</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>7</v>
@@ -3852,13 +3855,13 @@
         <v>45778</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E193" s="4" t="n">
         <v>912</v>
@@ -3869,13 +3872,13 @@
         <v>45778</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E194" s="4" t="n">
         <v>1762</v>
@@ -3886,7 +3889,7 @@
         <v>45778</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>6</v>
@@ -3906,7 +3909,7 @@
         <v>5</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>7</v>
@@ -3923,7 +3926,7 @@
         <v>5</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>7</v>
@@ -3937,7 +3940,7 @@
         <v>45778</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>6</v>
@@ -3954,10 +3957,10 @@
         <v>45778</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>7</v>
@@ -3974,10 +3977,10 @@
         <v>5</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E200" s="4" t="n">
         <v>2417</v>
@@ -3988,13 +3991,13 @@
         <v>45778</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E201" s="4" t="n">
         <v>1900</v>
@@ -4005,7 +4008,7 @@
         <v>45778</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>6</v>
@@ -4022,10 +4025,10 @@
         <v>45778</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>7</v>
@@ -4039,13 +4042,13 @@
         <v>45778</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E204" s="4" t="n">
         <v>870</v>
@@ -4056,13 +4059,13 @@
         <v>45778</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E205" s="4" t="n">
         <v>759</v>
@@ -4073,7 +4076,7 @@
         <v>45778</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>6</v>
@@ -4090,7 +4093,7 @@
         <v>45778</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>6</v>
@@ -4107,10 +4110,10 @@
         <v>45413</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>7</v>
@@ -4130,7 +4133,7 @@
         <v>6</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E209" s="4" t="n">
         <v>1790</v>
@@ -4141,10 +4144,10 @@
         <v>45413</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>7</v>
@@ -4158,13 +4161,13 @@
         <v>45413</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E211" s="4" t="n">
         <v>1870</v>
@@ -4178,7 +4181,7 @@
         <v>5</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>7</v>
@@ -4192,13 +4195,13 @@
         <v>45413</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E213" s="4" t="n">
         <v>1610</v>
@@ -4209,7 +4212,7 @@
         <v>45413</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>6</v>
@@ -4232,7 +4235,7 @@
         <v>6</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E215" s="4" t="n">
         <v>1450</v>
@@ -4243,10 +4246,10 @@
         <v>45413</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>7</v>
@@ -4260,13 +4263,13 @@
         <v>45413</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E217" s="4" t="n">
         <v>0</v>
@@ -4280,7 +4283,7 @@
         <v>5</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>7</v>
@@ -4294,13 +4297,13 @@
         <v>45413</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E219" s="4" t="n">
         <v>2690</v>
@@ -4311,7 +4314,7 @@
         <v>45413</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>6</v>
@@ -4328,13 +4331,13 @@
         <v>45413</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E221" s="4" t="n">
         <v>2490</v>
@@ -4362,13 +4365,13 @@
         <v>45413</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E223" s="4" t="n">
         <v>2910</v>
@@ -4379,7 +4382,7 @@
         <v>45413</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>6</v>
@@ -4396,13 +4399,13 @@
         <v>45413</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E225" s="4" t="n">
         <v>1380</v>
@@ -4416,7 +4419,7 @@
         <v>5</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>7</v>
@@ -4433,7 +4436,7 @@
         <v>5</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>7</v>
@@ -4450,10 +4453,10 @@
         <v>5</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E228" s="4" t="n">
         <v>1972</v>
@@ -4467,10 +4470,10 @@
         <v>5</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E229" s="4" t="n">
         <v>2697</v>
@@ -4521,7 +4524,7 @@
         <v>6</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E232" s="4" t="n">
         <v>1819</v>
@@ -4538,7 +4541,7 @@
         <v>6</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E233" s="4" t="n">
         <v>2786</v>
@@ -4549,10 +4552,10 @@
         <v>45047</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>7</v>
@@ -4566,10 +4569,10 @@
         <v>45047</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>7</v>
@@ -4583,13 +4586,13 @@
         <v>45047</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E236" s="4" t="n">
         <v>1915</v>
@@ -4600,13 +4603,13 @@
         <v>45047</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E237" s="4" t="n">
         <v>2537</v>
@@ -4617,7 +4620,7 @@
         <v>45047</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>6</v>
@@ -4634,7 +4637,7 @@
         <v>45047</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>6</v>
@@ -4651,13 +4654,13 @@
         <v>45047</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E240" s="4" t="n">
         <v>1661</v>
@@ -4668,13 +4671,13 @@
         <v>45047</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E241" s="4" t="n">
         <v>2446</v>
@@ -4685,10 +4688,10 @@
         <v>45047</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>7</v>
@@ -4702,10 +4705,10 @@
         <v>45047</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>7</v>
@@ -4719,13 +4722,13 @@
         <v>45047</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E244" s="4" t="n">
         <v>2034</v>
@@ -4736,13 +4739,13 @@
         <v>45047</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E245" s="4" t="n">
         <v>2629</v>
@@ -4753,7 +4756,7 @@
         <v>45047</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>6</v>
@@ -4770,7 +4773,7 @@
         <v>45047</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>6</v>
@@ -4787,13 +4790,13 @@
         <v>45047</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E248" s="4" t="n">
         <v>1711</v>
@@ -4804,13 +4807,13 @@
         <v>45047</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E249" s="4" t="n">
         <v>2523</v>
@@ -4821,7 +4824,7 @@
         <v>45809</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>6</v>
@@ -4838,13 +4841,13 @@
         <v>45809</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E251" s="4" t="n">
         <v>2054</v>
@@ -4855,10 +4858,10 @@
         <v>45809</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>7</v>
@@ -4872,13 +4875,13 @@
         <v>45809</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E253" s="4" t="n">
         <v>1543</v>
@@ -4892,7 +4895,7 @@
         <v>5</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>7</v>
@@ -4906,13 +4909,13 @@
         <v>45809</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E255" s="4" t="n">
         <v>2518</v>
@@ -4940,13 +4943,13 @@
         <v>45809</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E257" s="4" t="n">
         <v>2450</v>
@@ -4957,13 +4960,13 @@
         <v>45809</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C258" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D258" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="E258" s="4" t="n">
         <v>2080</v>
@@ -4974,13 +4977,13 @@
         <v>45809</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E259" s="4" t="n">
         <v>1950</v>
@@ -4991,7 +4994,7 @@
         <v>45809</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>6</v>
@@ -5011,7 +5014,7 @@
         <v>5</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D261" s="3" t="s">
         <v>7</v>
@@ -5028,10 +5031,10 @@
         <v>5</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E262" s="4" t="n">
         <v>5</v>
@@ -5045,10 +5048,10 @@
         <v>5</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E263" s="4" t="n">
         <v>2240</v>
@@ -5059,13 +5062,13 @@
         <v>45444</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E264" s="4" t="n">
         <v>1960</v>
@@ -5076,7 +5079,7 @@
         <v>45444</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>6</v>
@@ -5096,10 +5099,10 @@
         <v>5</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E266" s="4" t="n">
         <v>1740</v>
@@ -5110,7 +5113,7 @@
         <v>45444</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>6</v>
@@ -5127,13 +5130,13 @@
         <v>45444</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E268" s="4" t="n">
         <v>1870</v>
@@ -5161,13 +5164,13 @@
         <v>45444</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E270" s="4" t="n">
         <v>1510</v>
@@ -5178,7 +5181,7 @@
         <v>45444</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C271" s="3" t="s">
         <v>6</v>
@@ -5198,10 +5201,10 @@
         <v>5</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E272" s="4" t="n">
         <v>670</v>
@@ -5212,7 +5215,7 @@
         <v>45444</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>6</v>
@@ -5229,13 +5232,13 @@
         <v>45444</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E274" s="4" t="n">
         <v>2170</v>
@@ -5246,10 +5249,10 @@
         <v>45444</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D275" s="3" t="s">
         <v>7</v>
@@ -5269,7 +5272,7 @@
         <v>6</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E276" s="4" t="n">
         <v>2490</v>
@@ -5280,13 +5283,13 @@
         <v>45444</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E277" s="4" t="n">
         <v>1650</v>
@@ -5297,10 +5300,10 @@
         <v>45444</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D278" s="3" t="s">
         <v>7</v>
@@ -5314,13 +5317,13 @@
         <v>45444</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E279" s="4" t="n">
         <v>1420</v>
@@ -5331,10 +5334,10 @@
         <v>45444</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>7</v>
@@ -5354,7 +5357,7 @@
         <v>6</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E281" s="4" t="n">
         <v>99999</v>
@@ -5368,7 +5371,7 @@
         <v>5</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>7</v>
@@ -5385,7 +5388,7 @@
         <v>5</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>7</v>
@@ -5402,10 +5405,10 @@
         <v>5</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E284" s="4" t="n">
         <v>2039</v>
@@ -5419,10 +5422,10 @@
         <v>5</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E285" s="4" t="n">
         <v>2775</v>
@@ -5473,7 +5476,7 @@
         <v>6</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E288" s="4" t="n">
         <v>1873</v>
@@ -5490,7 +5493,7 @@
         <v>6</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E289" s="4" t="n">
         <v>2839</v>
@@ -5501,10 +5504,10 @@
         <v>45078</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>7</v>
@@ -5518,10 +5521,10 @@
         <v>45078</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>7</v>
@@ -5535,13 +5538,13 @@
         <v>45078</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E292" s="4" t="n">
         <v>1967</v>
@@ -5552,13 +5555,13 @@
         <v>45078</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E293" s="4" t="n">
         <v>2589</v>
@@ -5569,7 +5572,7 @@
         <v>45078</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>6</v>
@@ -5586,7 +5589,7 @@
         <v>45078</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>6</v>
@@ -5603,13 +5606,13 @@
         <v>45078</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E296" s="4" t="n">
         <v>1729</v>
@@ -5620,13 +5623,13 @@
         <v>45078</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C297" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E297" s="4" t="n">
         <v>2498</v>
@@ -5637,10 +5640,10 @@
         <v>45078</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>7</v>
@@ -5654,10 +5657,10 @@
         <v>45078</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>7</v>
@@ -5671,13 +5674,13 @@
         <v>45078</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E300" s="4" t="n">
         <v>2108</v>
@@ -5688,13 +5691,13 @@
         <v>45078</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E301" s="4" t="n">
         <v>2719</v>
@@ -5705,7 +5708,7 @@
         <v>45078</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C302" s="3" t="s">
         <v>6</v>
@@ -5722,7 +5725,7 @@
         <v>45078</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C303" s="3" t="s">
         <v>6</v>
@@ -5739,13 +5742,13 @@
         <v>45078</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E304" s="4" t="n">
         <v>1788</v>
@@ -5756,13 +5759,13 @@
         <v>45078</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E305" s="4" t="n">
         <v>2594</v>
@@ -5790,7 +5793,7 @@
         <v>45839</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>6</v>
@@ -5810,7 +5813,7 @@
         <v>5</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D308" s="3" t="s">
         <v>7</v>
@@ -5824,7 +5827,7 @@
         <v>45839</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>6</v>
@@ -5841,13 +5844,13 @@
         <v>45839</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E310" s="4" t="n">
         <v>2780</v>
@@ -5858,13 +5861,13 @@
         <v>45839</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E311" s="4" t="n">
         <v>2116</v>
@@ -5875,13 +5878,13 @@
         <v>45839</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E312" s="4" t="n">
         <v>2256</v>
@@ -5895,10 +5898,10 @@
         <v>5</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E313" s="4" t="n">
         <v>1650</v>
@@ -5915,7 +5918,7 @@
         <v>6</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E314" s="4" t="n">
         <v>1760</v>
@@ -5926,10 +5929,10 @@
         <v>45839</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D315" s="3" t="s">
         <v>7</v>
@@ -5946,10 +5949,10 @@
         <v>5</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E316" s="4" t="n">
         <v>150</v>
@@ -5960,13 +5963,13 @@
         <v>45839</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E317" s="4" t="n">
         <v>2390</v>
@@ -5977,7 +5980,7 @@
         <v>45839</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>6</v>
@@ -5994,10 +5997,10 @@
         <v>45839</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D319" s="3" t="s">
         <v>7</v>
@@ -6011,10 +6014,10 @@
         <v>45474</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D320" s="3" t="s">
         <v>7</v>
@@ -6028,13 +6031,13 @@
         <v>45474</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C321" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E321" s="4" t="n">
         <v>1790</v>
@@ -6048,7 +6051,7 @@
         <v>5</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D322" s="3" t="s">
         <v>7</v>
@@ -6062,13 +6065,13 @@
         <v>45474</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E323" s="4" t="n">
         <v>1680</v>
@@ -6079,10 +6082,10 @@
         <v>45474</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D324" s="3" t="s">
         <v>7</v>
@@ -6096,13 +6099,13 @@
         <v>45474</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E325" s="4" t="n">
         <v>1530</v>
@@ -6113,13 +6116,13 @@
         <v>45474</v>
       </c>
       <c r="B326" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D326" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="C326" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D326" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="E326" s="4" t="n">
         <v>2290</v>
@@ -6130,13 +6133,13 @@
         <v>45474</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C327" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E327" s="4" t="n">
         <v>1960</v>
@@ -6150,7 +6153,7 @@
         <v>5</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>7</v>
@@ -6164,13 +6167,13 @@
         <v>45474</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C329" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E329" s="4" t="n">
         <v>0</v>
@@ -6181,10 +6184,10 @@
         <v>45474</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>7</v>
@@ -6204,7 +6207,7 @@
         <v>6</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E331" s="4" t="n">
         <v>980</v>
@@ -6215,10 +6218,10 @@
         <v>45474</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D332" s="3" t="s">
         <v>7</v>
@@ -6232,13 +6235,13 @@
         <v>45474</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E333" s="4" t="n">
         <v>1870</v>
@@ -6249,13 +6252,13 @@
         <v>45474</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C334" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E334" s="4" t="n">
         <v>2540</v>
@@ -6266,7 +6269,7 @@
         <v>45474</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C335" s="3" t="s">
         <v>6</v>
@@ -6286,7 +6289,7 @@
         <v>5</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D336" s="3" t="s">
         <v>7</v>
@@ -6300,13 +6303,13 @@
         <v>45474</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E337" s="4" t="n">
         <v>1750</v>
@@ -6317,10 +6320,10 @@
         <v>45474</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>7</v>
@@ -6334,13 +6337,13 @@
         <v>45474</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C339" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E339" s="4" t="n">
         <v>1</v>
@@ -6351,13 +6354,13 @@
         <v>45658</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C340" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E340" s="4" t="n">
         <v>1830</v>
@@ -6368,10 +6371,10 @@
         <v>45658</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D341" s="3" t="s">
         <v>7</v>
@@ -6385,13 +6388,13 @@
         <v>45658</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C342" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E342" s="4" t="n">
         <v>1670</v>
@@ -6405,7 +6408,7 @@
         <v>5</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D343" s="3" t="s">
         <v>7</v>
@@ -6422,7 +6425,7 @@
         <v>5</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>7</v>
@@ -6439,10 +6442,10 @@
         <v>5</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E345" s="4" t="n">
         <v>2387</v>
@@ -6456,10 +6459,10 @@
         <v>5</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E346" s="4" t="n">
         <v>1925</v>
@@ -6510,7 +6513,7 @@
         <v>6</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E349" s="4" t="n">
         <v>2541</v>
@@ -6527,7 +6530,7 @@
         <v>6</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E350" s="4" t="n">
         <v>1462</v>
@@ -6538,10 +6541,10 @@
         <v>46023</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D351" s="3" t="s">
         <v>7</v>
@@ -6555,10 +6558,10 @@
         <v>46023</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D352" s="3" t="s">
         <v>7</v>
@@ -6572,13 +6575,13 @@
         <v>46023</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E353" s="4" t="n">
         <v>2217</v>
@@ -6589,13 +6592,13 @@
         <v>46023</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E354" s="4" t="n">
         <v>1958</v>
@@ -6606,7 +6609,7 @@
         <v>46023</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>6</v>
@@ -6623,7 +6626,7 @@
         <v>46023</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C356" s="3" t="s">
         <v>6</v>
@@ -6640,13 +6643,13 @@
         <v>46023</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C357" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E357" s="4" t="n">
         <v>2094</v>
@@ -6657,13 +6660,13 @@
         <v>46023</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C358" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E358" s="4" t="n">
         <v>1721</v>
@@ -6674,10 +6677,10 @@
         <v>46023</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D359" s="3" t="s">
         <v>7</v>
@@ -6691,10 +6694,10 @@
         <v>46023</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>7</v>
@@ -6708,13 +6711,13 @@
         <v>46023</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E361" s="4" t="n">
         <v>2369</v>
@@ -6725,13 +6728,13 @@
         <v>46023</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E362" s="4" t="n">
         <v>2013</v>
@@ -6742,7 +6745,7 @@
         <v>46023</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C363" s="3" t="s">
         <v>6</v>
@@ -6759,7 +6762,7 @@
         <v>46023</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C364" s="3" t="s">
         <v>6</v>
@@ -6776,13 +6779,13 @@
         <v>46023</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C365" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E365" s="4" t="n">
         <v>2187</v>
@@ -6793,13 +6796,13 @@
         <v>46023</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C366" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E366" s="4" t="n">
         <v>1635</v>
@@ -6810,13 +6813,13 @@
         <v>45658</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C367" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E367" s="4" t="n">
         <v>1383</v>
@@ -6827,13 +6830,13 @@
         <v>45658</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C368" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E368" s="4" t="n">
         <v>1349</v>
@@ -6844,13 +6847,13 @@
         <v>45658</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C369" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E369" s="4" t="n">
         <v>2773</v>
@@ -6867,7 +6870,7 @@
         <v>6</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E370" s="4" t="n">
         <v>2685</v>
@@ -6881,7 +6884,7 @@
         <v>5</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>7</v>
@@ -6898,7 +6901,7 @@
         <v>5</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D372" s="3" t="s">
         <v>7</v>
@@ -6915,10 +6918,10 @@
         <v>5</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E373" s="4" t="n">
         <v>0</v>
@@ -6929,13 +6932,13 @@
         <v>45658</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E374" s="4" t="n">
         <v>159</v>
@@ -6946,7 +6949,7 @@
         <v>45658</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C375" s="3" t="s">
         <v>6</v>
@@ -6963,7 +6966,7 @@
         <v>45658</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C376" s="3" t="s">
         <v>6</v>
@@ -6983,7 +6986,7 @@
         <v>5</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>7</v>
@@ -6997,13 +7000,13 @@
         <v>45292</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C378" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E378" s="4" t="n">
         <v>2340</v>
@@ -7014,10 +7017,10 @@
         <v>45292</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D379" s="3" t="s">
         <v>7</v>
@@ -7037,7 +7040,7 @@
         <v>6</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E380" s="4" t="n">
         <v>2780</v>
@@ -7048,10 +7051,10 @@
         <v>45292</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>7</v>
@@ -7065,13 +7068,13 @@
         <v>45292</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C382" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E382" s="4" t="n">
         <v>2190</v>
@@ -7085,7 +7088,7 @@
         <v>5</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D383" s="3" t="s">
         <v>7</v>
@@ -7099,13 +7102,13 @@
         <v>45292</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C384" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E384" s="4" t="n">
         <v>2010</v>
@@ -7116,10 +7119,10 @@
         <v>45292</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D385" s="3" t="s">
         <v>7</v>
@@ -7136,10 +7139,10 @@
         <v>5</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E386" s="4" t="n">
         <v>0</v>
@@ -7150,7 +7153,7 @@
         <v>45292</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C387" s="3" t="s">
         <v>6</v>
@@ -7167,13 +7170,13 @@
         <v>45292</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E388" s="4" t="n">
         <v>1990</v>
@@ -7201,13 +7204,13 @@
         <v>45292</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C390" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E390" s="4" t="n">
         <v>1670</v>
@@ -7218,13 +7221,13 @@
         <v>45292</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E391" s="4" t="n">
         <v>2430</v>
@@ -7235,7 +7238,7 @@
         <v>45292</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C392" s="3" t="s">
         <v>6</v>
@@ -7255,10 +7258,10 @@
         <v>5</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E393" s="4" t="n">
         <v>2760</v>
@@ -7272,7 +7275,7 @@
         <v>5</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>7</v>
@@ -7289,7 +7292,7 @@
         <v>5</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>7</v>
@@ -7306,7 +7309,7 @@
         <v>5</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D396" s="3" t="s">
         <v>7</v>
@@ -7323,7 +7326,7 @@
         <v>5</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D397" s="3" t="s">
         <v>7</v>
@@ -7340,10 +7343,10 @@
         <v>5</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E398" s="4" t="n">
         <v>1934</v>
@@ -7357,10 +7360,10 @@
         <v>5</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E399" s="4" t="n">
         <v>2148</v>
@@ -7374,10 +7377,10 @@
         <v>5</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E400" s="4" t="n">
         <v>1726</v>
@@ -7391,10 +7394,10 @@
         <v>5</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E401" s="4" t="n">
         <v>2395</v>
@@ -7445,7 +7448,7 @@
         <v>6</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E404" s="4" t="n">
         <v>1368</v>
@@ -7462,7 +7465,7 @@
         <v>6</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E405" s="4" t="n">
         <v>2574</v>
@@ -7473,10 +7476,10 @@
         <v>44927</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D406" s="3" t="s">
         <v>7</v>
@@ -7490,10 +7493,10 @@
         <v>44927</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D407" s="3" t="s">
         <v>7</v>
@@ -7507,13 +7510,13 @@
         <v>44927</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E408" s="4" t="n">
         <v>1827</v>
@@ -7524,13 +7527,13 @@
         <v>44927</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E409" s="4" t="n">
         <v>2389</v>
@@ -7541,7 +7544,7 @@
         <v>44927</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>6</v>
@@ -7558,7 +7561,7 @@
         <v>44927</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>6</v>
@@ -7575,13 +7578,13 @@
         <v>44927</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C412" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E412" s="4" t="n">
         <v>1415</v>
@@ -7592,13 +7595,13 @@
         <v>44927</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C413" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E413" s="4" t="n">
         <v>2316</v>
@@ -7609,10 +7612,10 @@
         <v>44927</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>7</v>
@@ -7626,10 +7629,10 @@
         <v>44927</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D415" s="3" t="s">
         <v>7</v>
@@ -7643,13 +7646,13 @@
         <v>44927</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E416" s="4" t="n">
         <v>1974</v>
@@ -7660,13 +7663,13 @@
         <v>44927</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E417" s="4" t="n">
         <v>2468</v>
@@ -7677,7 +7680,7 @@
         <v>44927</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>6</v>
@@ -7694,7 +7697,7 @@
         <v>44927</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>6</v>
@@ -7711,13 +7714,13 @@
         <v>44927</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C420" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E420" s="4" t="n">
         <v>1523</v>
@@ -7728,13 +7731,13 @@
         <v>44927</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E421" s="4" t="n">
         <v>2431</v>
@@ -7748,7 +7751,7 @@
         <v>5</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>7</v>
@@ -7765,7 +7768,7 @@
         <v>5</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D423" s="3" t="s">
         <v>7</v>
@@ -7782,10 +7785,10 @@
         <v>5</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E424" s="4" t="n">
         <v>2475</v>
@@ -7799,10 +7802,10 @@
         <v>5</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E425" s="4" t="n">
         <v>2107</v>
@@ -7853,7 +7856,7 @@
         <v>6</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E428" s="4" t="n">
         <v>2593</v>
@@ -7870,7 +7873,7 @@
         <v>6</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E429" s="4" t="n">
         <v>1528</v>
@@ -7881,10 +7884,10 @@
         <v>46054</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D430" s="3" t="s">
         <v>7</v>
@@ -7898,10 +7901,10 @@
         <v>46054</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D431" s="3" t="s">
         <v>7</v>
@@ -7915,13 +7918,13 @@
         <v>46054</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>2296</v>
@@ -7932,13 +7935,13 @@
         <v>46054</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>2012</v>
@@ -7949,7 +7952,7 @@
         <v>46054</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C434" s="3" t="s">
         <v>6</v>
@@ -7966,7 +7969,7 @@
         <v>46054</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C435" s="3" t="s">
         <v>6</v>
@@ -7983,13 +7986,13 @@
         <v>46054</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C436" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E436" s="4" t="n">
         <v>2165</v>
@@ -8000,13 +8003,13 @@
         <v>46054</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C437" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E437" s="4" t="n">
         <v>1794</v>
@@ -8017,10 +8020,10 @@
         <v>46054</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D438" s="3" t="s">
         <v>7</v>
@@ -8034,10 +8037,10 @@
         <v>46054</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D439" s="3" t="s">
         <v>7</v>
@@ -8051,13 +8054,13 @@
         <v>46054</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E440" s="4" t="n">
         <v>2438</v>
@@ -8068,13 +8071,13 @@
         <v>46054</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E441" s="4" t="n">
         <v>2089</v>
@@ -8085,7 +8088,7 @@
         <v>46054</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C442" s="3" t="s">
         <v>6</v>
@@ -8102,7 +8105,7 @@
         <v>46054</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C443" s="3" t="s">
         <v>6</v>
@@ -8119,13 +8122,13 @@
         <v>46054</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C444" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E444" s="4" t="n">
         <v>2243</v>
@@ -8136,13 +8139,13 @@
         <v>46054</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C445" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E445" s="4" t="n">
         <v>1698</v>
@@ -8153,7 +8156,7 @@
         <v>45689</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C446" s="3" t="s">
         <v>6</v>
@@ -8170,13 +8173,13 @@
         <v>45689</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E447" s="4" t="n">
         <v>1817</v>
@@ -8187,7 +8190,7 @@
         <v>45689</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C448" s="3" t="s">
         <v>6</v>
@@ -8204,13 +8207,13 @@
         <v>45689</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C449" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E449" s="4" t="n">
         <v>2100</v>
@@ -8221,10 +8224,10 @@
         <v>45689</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D450" s="3" t="s">
         <v>7</v>
@@ -8238,13 +8241,13 @@
         <v>45689</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C451" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E451" s="4" t="n">
         <v>1741</v>
@@ -8255,13 +8258,13 @@
         <v>45689</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E452" s="4" t="n">
         <v>1411</v>
@@ -8272,13 +8275,13 @@
         <v>45689</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E453" s="4" t="n">
         <v>1872</v>
@@ -8306,7 +8309,7 @@
         <v>45689</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C455" s="3" t="s">
         <v>6</v>
@@ -8323,10 +8326,10 @@
         <v>45689</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
         <v>7</v>
@@ -8340,13 +8343,13 @@
         <v>45689</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C457" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E457" s="4" t="n">
         <v>2340</v>
@@ -8357,13 +8360,13 @@
         <v>45689</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C458" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E458" s="4" t="n">
         <v>2150</v>
@@ -8374,13 +8377,13 @@
         <v>45689</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C459" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E459" s="4" t="n">
         <v>1760</v>
@@ -8391,7 +8394,7 @@
         <v>45689</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C460" s="3" t="s">
         <v>6</v>
@@ -8411,7 +8414,7 @@
         <v>5</v>
       </c>
       <c r="C461" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D461" s="3" t="s">
         <v>7</v>
@@ -8425,13 +8428,13 @@
         <v>45689</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C462" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E462" s="4" t="n">
         <v>99999</v>
@@ -8442,13 +8445,13 @@
         <v>45689</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C463" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E463" s="4" t="n">
         <v>2560</v>
@@ -8476,13 +8479,13 @@
         <v>45323</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E465" s="4" t="n">
         <v>1890</v>
@@ -8493,7 +8496,7 @@
         <v>45323</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C466" s="3" t="s">
         <v>6</v>
@@ -8513,10 +8516,10 @@
         <v>5</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E467" s="4" t="n">
         <v>1760</v>
@@ -8527,7 +8530,7 @@
         <v>45323</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C468" s="3" t="s">
         <v>6</v>
@@ -8544,13 +8547,13 @@
         <v>45323</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E469" s="4" t="n">
         <v>1520</v>
@@ -8561,7 +8564,7 @@
         <v>45323</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C470" s="3" t="s">
         <v>6</v>
@@ -8584,7 +8587,7 @@
         <v>6</v>
       </c>
       <c r="D471" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E471" s="4" t="n">
         <v>1640</v>
@@ -8595,10 +8598,10 @@
         <v>45323</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D472" s="3" t="s">
         <v>7</v>
@@ -8612,13 +8615,13 @@
         <v>45323</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C473" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D473" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E473" s="4" t="n">
         <v>1300</v>
@@ -8632,7 +8635,7 @@
         <v>5</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D474" s="3" t="s">
         <v>7</v>
@@ -8646,13 +8649,13 @@
         <v>45323</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C475" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E475" s="4" t="n">
         <v>2230</v>
@@ -8663,7 +8666,7 @@
         <v>45323</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C476" s="3" t="s">
         <v>6</v>
@@ -8680,13 +8683,13 @@
         <v>45323</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C477" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D477" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E477" s="4" t="n">
         <v>2560</v>
@@ -8697,13 +8700,13 @@
         <v>45323</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C478" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D478" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E478" s="4" t="n">
         <v>1420</v>
@@ -8731,13 +8734,13 @@
         <v>45323</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E480" s="4" t="n">
         <v>1750</v>
@@ -8751,7 +8754,7 @@
         <v>5</v>
       </c>
       <c r="C481" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D481" s="3" t="s">
         <v>7</v>
@@ -8768,7 +8771,7 @@
         <v>5</v>
       </c>
       <c r="C482" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D482" s="3" t="s">
         <v>7</v>
@@ -8785,10 +8788,10 @@
         <v>5</v>
       </c>
       <c r="C483" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E483" s="4" t="n">
         <v>1861</v>
@@ -8802,10 +8805,10 @@
         <v>5</v>
       </c>
       <c r="C484" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E484" s="4" t="n">
         <v>2487</v>
@@ -8856,7 +8859,7 @@
         <v>6</v>
       </c>
       <c r="D487" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E487" s="4" t="n">
         <v>1697</v>
@@ -8873,7 +8876,7 @@
         <v>6</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E488" s="4" t="n">
         <v>2546</v>
@@ -8884,10 +8887,10 @@
         <v>44958</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C489" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D489" s="3" t="s">
         <v>7</v>
@@ -8901,10 +8904,10 @@
         <v>44958</v>
       </c>
       <c r="B490" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C490" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D490" s="3" t="s">
         <v>7</v>
@@ -8918,13 +8921,13 @@
         <v>44958</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C491" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E491" s="4" t="n">
         <v>1775</v>
@@ -8935,13 +8938,13 @@
         <v>44958</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C492" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E492" s="4" t="n">
         <v>2360</v>
@@ -8952,7 +8955,7 @@
         <v>44958</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C493" s="3" t="s">
         <v>6</v>
@@ -8969,7 +8972,7 @@
         <v>44958</v>
       </c>
       <c r="B494" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C494" s="3" t="s">
         <v>6</v>
@@ -8986,13 +8989,13 @@
         <v>44958</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C495" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E495" s="4" t="n">
         <v>1492</v>
@@ -9003,13 +9006,13 @@
         <v>44958</v>
       </c>
       <c r="B496" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C496" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E496" s="4" t="n">
         <v>2279</v>
@@ -9020,10 +9023,10 @@
         <v>44958</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C497" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D497" s="3" t="s">
         <v>7</v>
@@ -9037,10 +9040,10 @@
         <v>44958</v>
       </c>
       <c r="B498" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D498" s="3" t="s">
         <v>7</v>
@@ -9054,13 +9057,13 @@
         <v>44958</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E499" s="4" t="n">
         <v>1907</v>
@@ -9071,13 +9074,13 @@
         <v>44958</v>
       </c>
       <c r="B500" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E500" s="4" t="n">
         <v>2441</v>
@@ -9088,7 +9091,7 @@
         <v>44958</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C501" s="3" t="s">
         <v>6</v>
@@ -9105,7 +9108,7 @@
         <v>44958</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C502" s="3" t="s">
         <v>6</v>
@@ -9122,13 +9125,13 @@
         <v>44958</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C503" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E503" s="4" t="n">
         <v>1604</v>
@@ -9139,13 +9142,13 @@
         <v>44958</v>
       </c>
       <c r="B504" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C504" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E504" s="4" t="n">
         <v>2387</v>
@@ -9156,13 +9159,13 @@
         <v>45992</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E505" s="4" t="n">
         <v>1997</v>
@@ -9173,13 +9176,13 @@
         <v>45992</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E506" s="4" t="n">
         <v>2297</v>
@@ -9190,13 +9193,13 @@
         <v>45992</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C507" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E507" s="4" t="n">
         <v>2554</v>
@@ -9227,7 +9230,7 @@
         <v>5</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D509" s="3" t="s">
         <v>7</v>
@@ -9241,13 +9244,13 @@
         <v>45992</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E510" s="4" t="n">
         <v>2116</v>
@@ -9258,13 +9261,13 @@
         <v>45992</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C511" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E511" s="4" t="n">
         <v>2960</v>
@@ -9275,10 +9278,10 @@
         <v>45992</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D512" s="3" t="s">
         <v>7</v>
@@ -9292,7 +9295,7 @@
         <v>45992</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C513" s="3" t="s">
         <v>6</v>
@@ -9309,13 +9312,13 @@
         <v>45992</v>
       </c>
       <c r="B514" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C514" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D514" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E514" s="4" t="n">
         <v>2890</v>
@@ -9329,10 +9332,10 @@
         <v>5</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D515" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E515" s="4" t="n">
         <v>1750</v>
@@ -9346,10 +9349,10 @@
         <v>5</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D516" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E516" s="4" t="n">
         <v>2820</v>
@@ -9366,7 +9369,7 @@
         <v>6</v>
       </c>
       <c r="D517" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E517" s="4" t="n">
         <v>2190</v>
@@ -9380,7 +9383,7 @@
         <v>5</v>
       </c>
       <c r="C518" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D518" s="3" t="s">
         <v>7</v>
@@ -9394,13 +9397,13 @@
         <v>45627</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C519" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D519" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E519" s="4" t="n">
         <v>1940</v>
@@ -9411,10 +9414,10 @@
         <v>45627</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D520" s="3" t="s">
         <v>7</v>
@@ -9434,7 +9437,7 @@
         <v>6</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E521" s="4" t="n">
         <v>1830</v>
@@ -9445,10 +9448,10 @@
         <v>45627</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C522" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D522" s="3" t="s">
         <v>7</v>
@@ -9462,13 +9465,13 @@
         <v>45627</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D523" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E523" s="4" t="n">
         <v>1670</v>
@@ -9479,7 +9482,7 @@
         <v>45627</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C524" s="3" t="s">
         <v>6</v>
@@ -9496,13 +9499,13 @@
         <v>45627</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E525" s="4" t="n">
         <v>1520</v>
@@ -9530,13 +9533,13 @@
         <v>45627</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C527" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D527" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E527" s="4" t="n">
         <v>0</v>
@@ -9547,7 +9550,7 @@
         <v>45627</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C528" s="3" t="s">
         <v>6</v>
@@ -9567,10 +9570,10 @@
         <v>5</v>
       </c>
       <c r="C529" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E529" s="4" t="n">
         <v>480</v>
@@ -9581,7 +9584,7 @@
         <v>45627</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C530" s="3" t="s">
         <v>6</v>
@@ -9598,13 +9601,13 @@
         <v>45627</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C531" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D531" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E531" s="4" t="n">
         <v>1890</v>
@@ -9615,10 +9618,10 @@
         <v>45627</v>
       </c>
       <c r="B532" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C532" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D532" s="3" t="s">
         <v>7</v>
@@ -9632,13 +9635,13 @@
         <v>45627</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C533" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D533" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E533" s="4" t="n">
         <v>89</v>
@@ -9666,13 +9669,13 @@
         <v>45627</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E535" s="4" t="n">
         <v>2870</v>
@@ -9683,7 +9686,7 @@
         <v>45627</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C536" s="3" t="s">
         <v>6</v>
@@ -9700,13 +9703,13 @@
         <v>45627</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C537" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D537" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E537" s="4" t="n">
         <v>2310</v>
@@ -9720,10 +9723,10 @@
         <v>5</v>
       </c>
       <c r="C538" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D538" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E538" s="4" t="n">
         <v>1918</v>
@@ -9740,7 +9743,7 @@
         <v>6</v>
       </c>
       <c r="D539" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E539" s="4" t="n">
         <v>1470</v>
@@ -9754,7 +9757,7 @@
         <v>5</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D540" s="3" t="s">
         <v>7</v>
@@ -9768,10 +9771,10 @@
         <v>45870</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C541" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D541" s="3" t="s">
         <v>7</v>
@@ -9788,10 +9791,10 @@
         <v>5</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E542" s="4" t="n">
         <v>2505</v>
@@ -9802,13 +9805,13 @@
         <v>45870</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C543" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E543" s="4" t="n">
         <v>2370</v>
@@ -9819,7 +9822,7 @@
         <v>45870</v>
       </c>
       <c r="B544" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C544" s="3" t="s">
         <v>6</v>
@@ -9836,13 +9839,13 @@
         <v>45870</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C545" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D545" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E545" s="4" t="n">
         <v>2490</v>
@@ -9853,13 +9856,13 @@
         <v>45870</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C546" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D546" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E546" s="4" t="n">
         <v>1380</v>
@@ -9870,7 +9873,7 @@
         <v>45870</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C547" s="3" t="s">
         <v>6</v>
@@ -9887,10 +9890,10 @@
         <v>45870</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D548" s="3" t="s">
         <v>7</v>
@@ -9904,13 +9907,13 @@
         <v>45870</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C549" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D549" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E549" s="4" t="n">
         <v>2350</v>
@@ -9921,13 +9924,13 @@
         <v>45870</v>
       </c>
       <c r="B550" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C550" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E550" s="4" t="n">
         <v>2780</v>
@@ -9941,7 +9944,7 @@
         <v>5</v>
       </c>
       <c r="C551" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D551" s="3" t="s">
         <v>7</v>
@@ -9955,13 +9958,13 @@
         <v>45505</v>
       </c>
       <c r="B552" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C552" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D552" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E552" s="4" t="n">
         <v>1870</v>
@@ -9972,10 +9975,10 @@
         <v>45505</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C553" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D553" s="3" t="s">
         <v>7</v>
@@ -9995,7 +9998,7 @@
         <v>6</v>
       </c>
       <c r="D554" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E554" s="4" t="n">
         <v>1740</v>
@@ -10006,10 +10009,10 @@
         <v>45505</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C555" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D555" s="3" t="s">
         <v>7</v>
@@ -10023,13 +10026,13 @@
         <v>45505</v>
       </c>
       <c r="B556" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C556" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D556" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E556" s="4" t="n">
         <v>1580</v>
@@ -10040,13 +10043,13 @@
         <v>45505</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C557" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E557" s="4" t="n">
         <v>2350</v>
@@ -10057,13 +10060,13 @@
         <v>45505</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D558" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E558" s="4" t="n">
         <v>1920</v>
@@ -10091,13 +10094,13 @@
         <v>45505</v>
       </c>
       <c r="B560" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C560" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E560" s="4" t="n">
         <v>0</v>
@@ -10108,7 +10111,7 @@
         <v>45505</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C561" s="3" t="s">
         <v>6</v>
@@ -10125,13 +10128,13 @@
         <v>45505</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D562" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E562" s="4" t="n">
         <v>2100</v>
@@ -10159,7 +10162,7 @@
         <v>45505</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C564" s="3" t="s">
         <v>6</v>
@@ -10179,7 +10182,7 @@
         <v>5</v>
       </c>
       <c r="C565" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D565" s="3" t="s">
         <v>7</v>
@@ -10193,13 +10196,13 @@
         <v>45505</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C566" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D566" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E566" s="4" t="n">
         <v>2790</v>
@@ -10210,10 +10213,10 @@
         <v>45505</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C567" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D567" s="3" t="s">
         <v>7</v>
@@ -10227,7 +10230,7 @@
         <v>45505</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C568" s="3" t="s">
         <v>6</v>
@@ -10247,10 +10250,10 @@
         <v>5</v>
       </c>
       <c r="C569" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D569" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E569" s="4" t="n">
         <v>123456</v>
@@ -10264,7 +10267,7 @@
         <v>5</v>
       </c>
       <c r="C570" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D570" s="3" t="s">
         <v>7</v>
@@ -10281,7 +10284,7 @@
         <v>5</v>
       </c>
       <c r="C571" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D571" s="3" t="s">
         <v>7</v>
@@ -10298,10 +10301,10 @@
         <v>5</v>
       </c>
       <c r="C572" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D572" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E572" s="4" t="n">
         <v>2619</v>
@@ -10315,10 +10318,10 @@
         <v>5</v>
       </c>
       <c r="C573" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D573" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E573" s="4" t="n">
         <v>2234</v>
@@ -10369,7 +10372,7 @@
         <v>6</v>
       </c>
       <c r="D576" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E576" s="4" t="n">
         <v>2724</v>
@@ -10386,7 +10389,7 @@
         <v>6</v>
       </c>
       <c r="D577" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E577" s="4" t="n">
         <v>1639</v>
@@ -10397,10 +10400,10 @@
         <v>46113</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D578" s="3" t="s">
         <v>7</v>
@@ -10414,10 +10417,10 @@
         <v>46113</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C579" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D579" s="3" t="s">
         <v>7</v>
@@ -10431,13 +10434,13 @@
         <v>46113</v>
       </c>
       <c r="B580" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C580" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D580" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E580" s="4" t="n">
         <v>2438</v>
@@ -10448,13 +10451,13 @@
         <v>46113</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C581" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D581" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E581" s="4" t="n">
         <v>2135</v>
@@ -10465,7 +10468,7 @@
         <v>46113</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C582" s="3" t="s">
         <v>6</v>
@@ -10482,7 +10485,7 @@
         <v>46113</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C583" s="3" t="s">
         <v>6</v>
@@ -10499,13 +10502,13 @@
         <v>46113</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C584" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D584" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E584" s="4" t="n">
         <v>2297</v>
@@ -10516,13 +10519,13 @@
         <v>46113</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C585" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D585" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E585" s="4" t="n">
         <v>1893</v>
@@ -10533,10 +10536,10 @@
         <v>46113</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C586" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D586" s="3" t="s">
         <v>7</v>
@@ -10550,10 +10553,10 @@
         <v>46113</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C587" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D587" s="3" t="s">
         <v>7</v>
@@ -10567,13 +10570,13 @@
         <v>46113</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D588" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E588" s="4" t="n">
         <v>2582</v>
@@ -10584,13 +10587,13 @@
         <v>46113</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C589" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D589" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E589" s="4" t="n">
         <v>2204</v>
@@ -10601,7 +10604,7 @@
         <v>46113</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C590" s="3" t="s">
         <v>6</v>
@@ -10618,7 +10621,7 @@
         <v>46113</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C591" s="3" t="s">
         <v>6</v>
@@ -10635,13 +10638,13 @@
         <v>46113</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C592" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D592" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E592" s="4" t="n">
         <v>2365</v>
@@ -10652,13 +10655,13 @@
         <v>46113</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C593" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D593" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E593" s="4" t="n">
         <v>1817</v>
@@ -10672,7 +10675,7 @@
         <v>5</v>
       </c>
       <c r="C594" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D594" s="3" t="s">
         <v>7</v>
@@ -10686,13 +10689,13 @@
         <v>45748</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C595" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D595" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E595" s="4" t="n">
         <v>2618</v>
@@ -10709,7 +10712,7 @@
         <v>6</v>
       </c>
       <c r="D596" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E596" s="4" t="n">
         <v>2667</v>
@@ -10726,7 +10729,7 @@
         <v>6</v>
       </c>
       <c r="D597" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E597" s="4" t="n">
         <v>1419</v>
@@ -10737,13 +10740,13 @@
         <v>45748</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C598" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D598" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E598" s="4" t="n">
         <v>1702</v>
@@ -10754,13 +10757,13 @@
         <v>45748</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C599" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D599" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E599" s="4" t="n">
         <v>2783</v>
@@ -10771,13 +10774,13 @@
         <v>45748</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C600" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D600" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E600" s="4" t="n">
         <v>2161</v>
@@ -10788,13 +10791,13 @@
         <v>45748</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C601" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D601" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E601" s="4" t="n">
         <v>2612</v>
@@ -10825,7 +10828,7 @@
         <v>5</v>
       </c>
       <c r="C603" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D603" s="3" t="s">
         <v>7</v>
@@ -10845,7 +10848,7 @@
         <v>6</v>
       </c>
       <c r="D604" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E604" s="4" t="n">
         <v>2854</v>
@@ -10856,13 +10859,13 @@
         <v>45748</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C605" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D605" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E605" s="4" t="n">
         <v>2576</v>
@@ -10893,10 +10896,10 @@
         <v>5</v>
       </c>
       <c r="C607" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D607" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E607" s="4" t="n">
         <v>2310</v>
@@ -10907,13 +10910,13 @@
         <v>45748</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C608" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D608" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E608" s="4" t="n">
         <v>1490</v>
@@ -10941,7 +10944,7 @@
         <v>45748</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C610" s="3" t="s">
         <v>6</v>
@@ -10958,13 +10961,13 @@
         <v>45748</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C611" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D611" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E611" s="4" t="n">
         <v>1</v>
@@ -10975,13 +10978,13 @@
         <v>45748</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C612" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D612" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E612" s="4" t="n">
         <v>2930</v>
@@ -10992,13 +10995,13 @@
         <v>45383</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C613" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D613" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E613" s="4" t="n">
         <v>2290</v>
@@ -11012,7 +11015,7 @@
         <v>5</v>
       </c>
       <c r="C614" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D614" s="3" t="s">
         <v>7</v>
@@ -11026,13 +11029,13 @@
         <v>45383</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C615" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D615" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E615" s="4" t="n">
         <v>2810</v>
@@ -11043,10 +11046,10 @@
         <v>45383</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C616" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>7</v>
@@ -11066,7 +11069,7 @@
         <v>6</v>
       </c>
       <c r="D617" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E617" s="4" t="n">
         <v>2370</v>
@@ -11077,10 +11080,10 @@
         <v>45383</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C618" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D618" s="3" t="s">
         <v>7</v>
@@ -11094,13 +11097,13 @@
         <v>45383</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C619" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D619" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E619" s="4" t="n">
         <v>2620</v>
@@ -11111,10 +11114,10 @@
         <v>45383</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C620" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D620" s="3" t="s">
         <v>7</v>
@@ -11145,7 +11148,7 @@
         <v>45383</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C622" s="3" t="s">
         <v>6</v>
@@ -11162,13 +11165,13 @@
         <v>45383</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C623" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D623" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E623" s="4" t="n">
         <v>1100</v>
@@ -11179,10 +11182,10 @@
         <v>45383</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C624" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D624" s="3" t="s">
         <v>7</v>
@@ -11199,10 +11202,10 @@
         <v>5</v>
       </c>
       <c r="C625" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D625" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E625" s="4" t="n">
         <v>1670</v>
@@ -11213,13 +11216,13 @@
         <v>45383</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C626" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D626" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E626" s="4" t="n">
         <v>2440</v>
@@ -11230,10 +11233,10 @@
         <v>45383</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C627" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D627" s="3" t="s">
         <v>7</v>
@@ -11250,10 +11253,10 @@
         <v>5</v>
       </c>
       <c r="C628" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D628" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E628" s="4" t="n">
         <v>2870</v>
@@ -11264,13 +11267,13 @@
         <v>45383</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C629" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D629" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E629" s="4" t="n">
         <v>1530</v>
@@ -11284,7 +11287,7 @@
         <v>5</v>
       </c>
       <c r="C630" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D630" s="3" t="s">
         <v>7</v>
@@ -11301,7 +11304,7 @@
         <v>5</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D631" s="3" t="s">
         <v>7</v>
@@ -11318,10 +11321,10 @@
         <v>5</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D632" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E632" s="4" t="n">
         <v>1939</v>
@@ -11335,10 +11338,10 @@
         <v>5</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D633" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E633" s="4" t="n">
         <v>2634</v>
@@ -11389,7 +11392,7 @@
         <v>6</v>
       </c>
       <c r="D636" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E636" s="4" t="n">
         <v>1781</v>
@@ -11406,7 +11409,7 @@
         <v>6</v>
       </c>
       <c r="D637" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E637" s="4" t="n">
         <v>2715</v>
@@ -11417,10 +11420,10 @@
         <v>45017</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D638" s="3" t="s">
         <v>7</v>
@@ -11434,10 +11437,10 @@
         <v>45017</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D639" s="3" t="s">
         <v>7</v>
@@ -11451,13 +11454,13 @@
         <v>45017</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D640" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E640" s="4" t="n">
         <v>1876</v>
@@ -11468,13 +11471,13 @@
         <v>45017</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D641" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E641" s="4" t="n">
         <v>2478</v>
@@ -11485,7 +11488,7 @@
         <v>45017</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C642" s="3" t="s">
         <v>6</v>
@@ -11502,7 +11505,7 @@
         <v>45017</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C643" s="3" t="s">
         <v>6</v>
@@ -11519,13 +11522,13 @@
         <v>45017</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C644" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D644" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E644" s="4" t="n">
         <v>1617</v>
@@ -11536,13 +11539,13 @@
         <v>45017</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C645" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D645" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E645" s="4" t="n">
         <v>2394</v>
@@ -11553,10 +11556,10 @@
         <v>45017</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D646" s="3" t="s">
         <v>7</v>
@@ -11570,10 +11573,10 @@
         <v>45017</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D647" s="3" t="s">
         <v>7</v>
@@ -11587,13 +11590,13 @@
         <v>45017</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D648" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E648" s="4" t="n">
         <v>1998</v>
@@ -11604,13 +11607,13 @@
         <v>45017</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D649" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E649" s="4" t="n">
         <v>2582</v>
@@ -11621,7 +11624,7 @@
         <v>45017</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C650" s="3" t="s">
         <v>6</v>
@@ -11638,7 +11641,7 @@
         <v>45017</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C651" s="3" t="s">
         <v>6</v>
@@ -11655,13 +11658,13 @@
         <v>45017</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C652" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D652" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E652" s="4" t="n">
         <v>1683</v>
@@ -11672,13 +11675,13 @@
         <v>45017</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C653" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D653" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E653" s="4" t="n">
         <v>2476</v>
@@ -11692,7 +11695,7 @@
         <v>5</v>
       </c>
       <c r="C654" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D654" s="3" t="s">
         <v>7</v>
@@ -11712,7 +11715,7 @@
         <v>6</v>
       </c>
       <c r="D655" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E655" s="4" t="n">
         <v>1980</v>
@@ -11723,10 +11726,10 @@
         <v>45689</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C656" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D656" s="3" t="s">
         <v>7</v>
@@ -11746,7 +11749,7 @@
         <v>6</v>
       </c>
       <c r="D657" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E657" s="4" t="n">
         <v>2100</v>
@@ -11757,10 +11760,10 @@
         <v>45047</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C658" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D658" s="3" t="s">
         <v>7</v>
@@ -11774,13 +11777,13 @@
         <v>45536</v>
       </c>
       <c r="B659" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C659" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D659" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E659" s="4" t="n">
         <v>2540</v>
@@ -11791,10 +11794,10 @@
         <v>44958</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C660" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D660" s="3" t="s">
         <v>7</v>
@@ -11811,10 +11814,10 @@
         <v>5</v>
       </c>
       <c r="C661" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D661" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E661" s="4" t="n">
         <v>2760</v>
@@ -11825,7 +11828,7 @@
         <v>44743</v>
       </c>
       <c r="B662" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C662" s="3" t="s">
         <v>6</v>
@@ -11842,7 +11845,7 @@
         <v>45078</v>
       </c>
       <c r="B663" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C663" s="3" t="s">
         <v>6</v>
@@ -11859,13 +11862,13 @@
         <v>45505</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C664" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D664" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E664" s="4" t="n">
         <v>1690</v>
@@ -11876,10 +11879,10 @@
         <v>45170</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D665" s="3" t="s">
         <v>7</v>
@@ -11893,10 +11896,10 @@
         <v>44835</v>
       </c>
       <c r="B666" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C666" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D666" s="3" t="s">
         <v>7</v>
@@ -11927,7 +11930,7 @@
         <v>44652</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C668" s="3" t="s">
         <v>6</v>
@@ -11947,13 +11950,13 @@
         <v>5</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D669" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E669" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="670" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11964,10 +11967,10 @@
         <v>5</v>
       </c>
       <c r="C670" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D670" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E670" s="4" t="n">
         <v>2143</v>
@@ -12001,10 +12004,10 @@
         <v>6</v>
       </c>
       <c r="D672" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E672" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="673" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12012,10 +12015,10 @@
         <v>44562</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C673" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D673" s="3" t="s">
         <v>7</v>
@@ -12029,16 +12032,16 @@
         <v>44562</v>
       </c>
       <c r="B674" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C674" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D674" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E674" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="675" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12046,7 +12049,7 @@
         <v>44562</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C675" s="3" t="s">
         <v>6</v>
@@ -12063,16 +12066,16 @@
         <v>44562</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C676" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D676" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E676" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12083,7 +12086,7 @@
         <v>5</v>
       </c>
       <c r="C677" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D677" s="3" t="s">
         <v>7</v>
@@ -12100,13 +12103,13 @@
         <v>5</v>
       </c>
       <c r="C678" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D678" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E678" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12123,7 +12126,7 @@
         <v>7</v>
       </c>
       <c r="E679" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="680" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12137,7 +12140,7 @@
         <v>6</v>
       </c>
       <c r="D680" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E680" s="4" t="n">
         <v>2075</v>
@@ -12148,16 +12151,16 @@
         <v>44593</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C681" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D681" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E681" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="682" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12165,13 +12168,13 @@
         <v>44593</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C682" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D682" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E682" s="4" t="n">
         <v>2129</v>
@@ -12182,7 +12185,7 @@
         <v>44593</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C683" s="3" t="s">
         <v>6</v>
@@ -12199,16 +12202,16 @@
         <v>44593</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C684" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D684" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E684" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="685" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12219,7 +12222,7 @@
         <v>5</v>
       </c>
       <c r="C685" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D685" s="3" t="s">
         <v>7</v>
@@ -12236,13 +12239,13 @@
         <v>5</v>
       </c>
       <c r="C686" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D686" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E686" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="687" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12259,7 +12262,7 @@
         <v>7</v>
       </c>
       <c r="E687" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="688" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12273,7 +12276,7 @@
         <v>6</v>
       </c>
       <c r="D688" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E688" s="4" t="n">
         <v>2142</v>
@@ -12284,10 +12287,10 @@
         <v>44621</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C689" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D689" s="3" t="s">
         <v>7</v>
@@ -12301,16 +12304,16 @@
         <v>44621</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C690" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D690" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E690" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="691" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12318,7 +12321,7 @@
         <v>44621</v>
       </c>
       <c r="B691" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C691" s="3" t="s">
         <v>6</v>
@@ -12327,7 +12330,7 @@
         <v>7</v>
       </c>
       <c r="E691" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="692" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12335,13 +12338,13 @@
         <v>44621</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C692" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E692" s="4" t="n">
         <v>2098</v>
@@ -12355,13 +12358,13 @@
         <v>5</v>
       </c>
       <c r="C693" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D693" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E693" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="694" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12372,10 +12375,10 @@
         <v>5</v>
       </c>
       <c r="C694" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D694" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E694" s="4" t="n">
         <v>2386</v>
@@ -12409,10 +12412,10 @@
         <v>6</v>
       </c>
       <c r="D696" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E696" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="697" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12420,10 +12423,10 @@
         <v>44652</v>
       </c>
       <c r="B697" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C697" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D697" s="3" t="s">
         <v>7</v>
@@ -12437,16 +12440,16 @@
         <v>44652</v>
       </c>
       <c r="B698" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C698" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D698" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E698" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="699" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12454,7 +12457,7 @@
         <v>44652</v>
       </c>
       <c r="B699" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C699" s="3" t="s">
         <v>6</v>
@@ -12471,16 +12474,16 @@
         <v>44652</v>
       </c>
       <c r="B700" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C700" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D700" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E700" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="701" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12491,7 +12494,7 @@
         <v>5</v>
       </c>
       <c r="C701" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D701" s="3" t="s">
         <v>7</v>
@@ -12508,13 +12511,13 @@
         <v>5</v>
       </c>
       <c r="C702" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D702" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E702" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="703" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12531,7 +12534,7 @@
         <v>7</v>
       </c>
       <c r="E703" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="704" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12545,7 +12548,7 @@
         <v>6</v>
       </c>
       <c r="D704" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E704" s="4" t="n">
         <v>2295</v>
@@ -12556,16 +12559,16 @@
         <v>44682</v>
       </c>
       <c r="B705" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C705" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D705" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E705" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="706" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12573,13 +12576,13 @@
         <v>44682</v>
       </c>
       <c r="B706" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C706" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D706" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E706" s="4" t="n">
         <v>2338</v>
@@ -12590,7 +12593,7 @@
         <v>44682</v>
       </c>
       <c r="B707" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C707" s="3" t="s">
         <v>6</v>
@@ -12607,16 +12610,16 @@
         <v>44682</v>
       </c>
       <c r="B708" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C708" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D708" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E708" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="709" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12627,13 +12630,13 @@
         <v>5</v>
       </c>
       <c r="C709" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D709" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E709" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="710" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12644,10 +12647,10 @@
         <v>5</v>
       </c>
       <c r="C710" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D710" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E710" s="4" t="n">
         <v>2527</v>
@@ -12681,10 +12684,10 @@
         <v>6</v>
       </c>
       <c r="D712" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E712" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12692,10 +12695,10 @@
         <v>44713</v>
       </c>
       <c r="B713" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C713" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D713" s="3" t="s">
         <v>7</v>
@@ -12709,16 +12712,16 @@
         <v>44713</v>
       </c>
       <c r="B714" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C714" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D714" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E714" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12726,7 +12729,7 @@
         <v>44713</v>
       </c>
       <c r="B715" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C715" s="3" t="s">
         <v>6</v>
@@ -12735,7 +12738,7 @@
         <v>7</v>
       </c>
       <c r="E715" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="716" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12743,13 +12746,13 @@
         <v>44713</v>
       </c>
       <c r="B716" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C716" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D716" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E716" s="4" t="n">
         <v>2284</v>
@@ -12763,7 +12766,7 @@
         <v>5</v>
       </c>
       <c r="C717" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D717" s="3" t="s">
         <v>7</v>
@@ -12780,13 +12783,13 @@
         <v>5</v>
       </c>
       <c r="C718" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D718" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E718" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="719" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12803,7 +12806,7 @@
         <v>7</v>
       </c>
       <c r="E719" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="720" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12817,7 +12820,7 @@
         <v>6</v>
       </c>
       <c r="D720" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E720" s="4" t="n">
         <v>2436</v>
@@ -12828,16 +12831,16 @@
         <v>44743</v>
       </c>
       <c r="B721" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C721" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D721" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E721" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="722" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12845,13 +12848,13 @@
         <v>44743</v>
       </c>
       <c r="B722" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C722" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D722" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E722" s="4" t="n">
         <v>2489</v>
@@ -12862,7 +12865,7 @@
         <v>44743</v>
       </c>
       <c r="B723" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C723" s="3" t="s">
         <v>6</v>
@@ -12879,16 +12882,16 @@
         <v>44743</v>
       </c>
       <c r="B724" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C724" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D724" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E724" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="725" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12899,13 +12902,13 @@
         <v>5</v>
       </c>
       <c r="C725" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D725" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E725" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="726" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12916,10 +12919,10 @@
         <v>5</v>
       </c>
       <c r="C726" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D726" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E726" s="4" t="n">
         <v>2661</v>
@@ -12953,10 +12956,10 @@
         <v>6</v>
       </c>
       <c r="D728" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E728" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="729" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12964,10 +12967,10 @@
         <v>44774</v>
       </c>
       <c r="B729" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C729" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D729" s="3" t="s">
         <v>7</v>
@@ -12981,16 +12984,16 @@
         <v>44774</v>
       </c>
       <c r="B730" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C730" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D730" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E730" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="731" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12998,7 +13001,7 @@
         <v>44774</v>
       </c>
       <c r="B731" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C731" s="3" t="s">
         <v>6</v>
@@ -13007,7 +13010,7 @@
         <v>7</v>
       </c>
       <c r="E731" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="732" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13015,13 +13018,13 @@
         <v>44774</v>
       </c>
       <c r="B732" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C732" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D732" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E732" s="4" t="n">
         <v>2396</v>
@@ -13035,7 +13038,7 @@
         <v>5</v>
       </c>
       <c r="C733" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D733" s="3" t="s">
         <v>7</v>
@@ -13052,13 +13055,13 @@
         <v>5</v>
       </c>
       <c r="C734" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D734" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E734" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="735" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13075,7 +13078,7 @@
         <v>7</v>
       </c>
       <c r="E735" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="736" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13089,7 +13092,7 @@
         <v>6</v>
       </c>
       <c r="D736" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E736" s="4" t="n">
         <v>2569</v>
@@ -13100,16 +13103,16 @@
         <v>44805</v>
       </c>
       <c r="B737" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C737" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D737" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E737" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="738" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13117,13 +13120,13 @@
         <v>44805</v>
       </c>
       <c r="B738" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C738" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D738" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E738" s="4" t="n">
         <v>2623</v>
@@ -13134,7 +13137,7 @@
         <v>44805</v>
       </c>
       <c r="B739" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C739" s="3" t="s">
         <v>6</v>
@@ -13151,16 +13154,16 @@
         <v>44805</v>
       </c>
       <c r="B740" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C740" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D740" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E740" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="741" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13171,13 +13174,13 @@
         <v>5</v>
       </c>
       <c r="C741" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D741" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E741" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="742" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13188,10 +13191,10 @@
         <v>5</v>
       </c>
       <c r="C742" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D742" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E742" s="4" t="n">
         <v>2795</v>
@@ -13225,10 +13228,10 @@
         <v>6</v>
       </c>
       <c r="D744" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E744" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="745" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13236,10 +13239,10 @@
         <v>44835</v>
       </c>
       <c r="B745" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C745" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D745" s="3" t="s">
         <v>7</v>
@@ -13253,16 +13256,16 @@
         <v>44835</v>
       </c>
       <c r="B746" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C746" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D746" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E746" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="747" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13270,7 +13273,7 @@
         <v>44835</v>
       </c>
       <c r="B747" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C747" s="3" t="s">
         <v>6</v>
@@ -13279,7 +13282,7 @@
         <v>7</v>
       </c>
       <c r="E747" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="748" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13287,13 +13290,13 @@
         <v>44835</v>
       </c>
       <c r="B748" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C748" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D748" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E748" s="4" t="n">
         <v>2524</v>
@@ -13307,7 +13310,7 @@
         <v>5</v>
       </c>
       <c r="C749" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D749" s="3" t="s">
         <v>7</v>
@@ -13324,13 +13327,13 @@
         <v>5</v>
       </c>
       <c r="C750" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D750" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E750" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="751" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13347,7 +13350,7 @@
         <v>7</v>
       </c>
       <c r="E751" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="752" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13361,7 +13364,7 @@
         <v>6</v>
       </c>
       <c r="D752" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E752" s="4" t="n">
         <v>2712</v>
@@ -13372,16 +13375,16 @@
         <v>44866</v>
       </c>
       <c r="B753" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C753" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D753" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E753" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="754" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13389,13 +13392,13 @@
         <v>44866</v>
       </c>
       <c r="B754" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C754" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D754" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E754" s="4" t="n">
         <v>2754</v>
@@ -13406,7 +13409,7 @@
         <v>44866</v>
       </c>
       <c r="B755" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C755" s="3" t="s">
         <v>6</v>
@@ -13423,16 +13426,16 @@
         <v>44866</v>
       </c>
       <c r="B756" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C756" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D756" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E756" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="757" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13443,13 +13446,13 @@
         <v>5</v>
       </c>
       <c r="C757" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D757" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E757" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="758" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13460,10 +13463,10 @@
         <v>5</v>
       </c>
       <c r="C758" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D758" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E758" s="4" t="n">
         <v>2931</v>
@@ -13497,10 +13500,10 @@
         <v>6</v>
       </c>
       <c r="D760" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E760" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="761" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13508,10 +13511,10 @@
         <v>44896</v>
       </c>
       <c r="B761" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C761" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D761" s="3" t="s">
         <v>7</v>
@@ -13525,16 +13528,16 @@
         <v>44896</v>
       </c>
       <c r="B762" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C762" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D762" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E762" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="763" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13542,7 +13545,7 @@
         <v>44896</v>
       </c>
       <c r="B763" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C763" s="3" t="s">
         <v>6</v>
@@ -13551,7 +13554,7 @@
         <v>7</v>
       </c>
       <c r="E763" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="764" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13559,13 +13562,13 @@
         <v>44896</v>
       </c>
       <c r="B764" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C764" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D764" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E764" s="4" t="n">
         <v>2665</v>
